--- a/Team-Data/2008-09/3-3-2008-09.xlsx
+++ b/Team-Data/2008-09/3-3-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>1.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>29</v>
@@ -769,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>16</v>
@@ -790,16 +857,16 @@
         <v>24</v>
       </c>
       <c r="AU2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
         <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>0.767</v>
+        <v>0.77</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>16.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.392</v>
+        <v>0.389</v>
       </c>
       <c r="O3" t="n">
         <v>20.2</v>
       </c>
       <c r="P3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.9</v>
@@ -903,10 +970,10 @@
         <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
         <v>23.3</v>
@@ -915,16 +982,16 @@
         <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.7</v>
+        <v>101.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -951,22 +1018,22 @@
         <v>20</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="n">
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -975,13 +1042,13 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW3" t="n">
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
         <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>0.426</v>
+        <v>0.417</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
@@ -1043,28 +1110,28 @@
         <v>34.5</v>
       </c>
       <c r="J4" t="n">
-        <v>76.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
         <v>16</v>
       </c>
       <c r="N4" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O4" t="n">
         <v>17.8</v>
       </c>
       <c r="P4" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.742</v>
+        <v>0.739</v>
       </c>
       <c r="R4" t="n">
         <v>10.8</v>
@@ -1079,7 +1146,7 @@
         <v>21</v>
       </c>
       <c r="V4" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
@@ -1091,22 +1158,22 @@
         <v>6.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
         <v>92.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
         <v>20</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
@@ -1145,16 +1212,16 @@
         <v>28</v>
       </c>
       <c r="AR4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
@@ -1163,7 +1230,7 @@
         <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1178,7 +1245,7 @@
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -1210,25 +1277,25 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.433</v>
+        <v>0.45</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J5" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
@@ -1237,16 +1304,16 @@
         <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.373</v>
+        <v>0.376</v>
       </c>
       <c r="O5" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.789</v>
+        <v>0.787</v>
       </c>
       <c r="R5" t="n">
         <v>12.1</v>
@@ -1258,13 +1325,13 @@
         <v>42.4</v>
       </c>
       <c r="U5" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="V5" t="n">
         <v>14.9</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
@@ -1276,28 +1343,28 @@
         <v>21.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.3</v>
+        <v>100.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2</v>
+        <v>-1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
@@ -1315,13 +1382,13 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP5" t="n">
         <v>14</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1336,31 +1403,31 @@
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV5" t="n">
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BB5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -1389,46 +1456,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
         <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.797</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
       <c r="O6" t="n">
         <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R6" t="n">
         <v>10.8</v>
@@ -1443,7 +1510,7 @@
         <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.7</v>
@@ -1455,19 +1522,19 @@
         <v>4.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.4</v>
+        <v>100.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1476,13 +1543,13 @@
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1494,22 +1561,22 @@
         <v>3</v>
       </c>
       <c r="AM6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
         <v>4</v>
       </c>
       <c r="AO6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>22</v>
       </c>
-      <c r="AP6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>21</v>
-      </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1521,25 +1588,25 @@
         <v>24</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1673,13 +1740,13 @@
         <v>10</v>
       </c>
       <c r="AL7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM7" t="n">
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO7" t="n">
         <v>24</v>
@@ -1694,13 +1761,13 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
         <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
@@ -1712,13 +1779,13 @@
         <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
         <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>0.639</v>
+        <v>0.65</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
@@ -1774,70 +1841,70 @@
         <v>78.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="L8" t="n">
         <v>6.4</v>
       </c>
       <c r="M8" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="N8" t="n">
         <v>0.362</v>
       </c>
       <c r="O8" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="P8" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="R8" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S8" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="T8" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U8" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V8" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>5.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z8" t="n">
         <v>22.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>102.8</v>
+        <v>102.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
         <v>6</v>
@@ -1846,7 +1913,7 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ8" t="n">
         <v>24</v>
@@ -1861,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,34 +1937,34 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
         <v>3</v>
       </c>
       <c r="AY8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>25</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>26</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
@@ -1906,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
         <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
@@ -1953,7 +2020,7 @@
         <v>35.8</v>
       </c>
       <c r="J9" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K9" t="n">
         <v>0.454</v>
@@ -1962,28 +2029,28 @@
         <v>4.6</v>
       </c>
       <c r="M9" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O9" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="P9" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
       <c r="R9" t="n">
         <v>10.8</v>
       </c>
       <c r="S9" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T9" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U9" t="n">
         <v>20.2</v>
@@ -1992,10 +2059,10 @@
         <v>11.9</v>
       </c>
       <c r="W9" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="X9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" t="n">
         <v>3.9</v>
@@ -2004,16 +2071,16 @@
         <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.3</v>
+        <v>93.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
@@ -2025,7 +2092,7 @@
         <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
         <v>24</v>
@@ -2049,16 +2116,16 @@
         <v>27</v>
       </c>
       <c r="AP9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR9" t="n">
         <v>18</v>
       </c>
       <c r="AS9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT9" t="n">
         <v>21</v>
@@ -2082,10 +2149,10 @@
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC9" t="n">
         <v>17</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
         <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>0.35</v>
+        <v>0.339</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
@@ -2135,7 +2202,7 @@
         <v>39.3</v>
       </c>
       <c r="J10" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K10" t="n">
         <v>0.459</v>
@@ -2147,31 +2214,31 @@
         <v>17.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.375</v>
+        <v>0.373</v>
       </c>
       <c r="O10" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="P10" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.781</v>
+        <v>0.783</v>
       </c>
       <c r="R10" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S10" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="T10" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U10" t="n">
         <v>20.8</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
         <v>8.199999999999999</v>
@@ -2183,31 +2250,31 @@
         <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.3</v>
+        <v>108.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.1</v>
+        <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2219,13 +2286,13 @@
         <v>11</v>
       </c>
       <c r="AL10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM10" t="n">
         <v>17</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2234,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR10" t="n">
         <v>9</v>
@@ -2258,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
         <v>24</v>
@@ -2270,7 +2337,7 @@
         <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -2299,64 +2366,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" t="n">
         <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.639</v>
+        <v>0.633</v>
       </c>
       <c r="H11" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J11" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L11" t="n">
         <v>7.8</v>
       </c>
       <c r="M11" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N11" t="n">
         <v>0.379</v>
       </c>
       <c r="O11" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="P11" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R11" t="n">
         <v>10.6</v>
       </c>
       <c r="S11" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T11" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U11" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V11" t="n">
         <v>14.2</v>
       </c>
       <c r="W11" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X11" t="n">
         <v>3.9</v>
@@ -2365,52 +2432,52 @@
         <v>5.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
         <v>20.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
       </c>
       <c r="AG11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
         <v>6</v>
       </c>
       <c r="AM11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
         <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2419,7 +2486,7 @@
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2428,13 +2495,13 @@
         <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV11" t="n">
         <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
@@ -2446,7 +2513,7 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -2481,22 +2548,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" t="n">
         <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>0.429</v>
+        <v>0.419</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J12" t="n">
         <v>86.3</v>
@@ -2505,13 +2572,13 @@
         <v>0.45</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M12" t="n">
         <v>21.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.376</v>
+        <v>0.373</v>
       </c>
       <c r="O12" t="n">
         <v>19.1</v>
@@ -2520,28 +2587,28 @@
         <v>23.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="R12" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S12" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T12" t="n">
         <v>43.7</v>
       </c>
       <c r="U12" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V12" t="n">
         <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y12" t="n">
         <v>5.6</v>
@@ -2553,16 +2620,16 @@
         <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.8</v>
+        <v>104.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2580,16 +2647,16 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
         <v>17</v>
@@ -2616,10 +2683,10 @@
         <v>22</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>28</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>26</v>
@@ -2756,7 +2823,7 @@
         <v>5</v>
       </c>
       <c r="AI13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2777,7 +2844,7 @@
         <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ13" t="n">
         <v>26</v>
@@ -2786,7 +2853,7 @@
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>22</v>
@@ -2798,7 +2865,7 @@
         <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2930,7 @@
         <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.476</v>
@@ -2872,10 +2939,10 @@
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.361</v>
+        <v>0.366</v>
       </c>
       <c r="O14" t="n">
         <v>20.6</v>
@@ -2884,55 +2951,55 @@
         <v>26.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R14" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T14" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W14" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
         <v>22.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.9</v>
+        <v>108.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>16</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2962,13 +3029,13 @@
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2983,10 +3050,10 @@
         <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
         <v>15</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>0.254</v>
+        <v>0.259</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
@@ -3045,7 +3112,7 @@
         <v>34.7</v>
       </c>
       <c r="J15" t="n">
-        <v>77.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0.448</v>
@@ -3057,16 +3124,16 @@
         <v>13.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.336</v>
+        <v>0.333</v>
       </c>
       <c r="O15" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P15" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.753</v>
+        <v>0.75</v>
       </c>
       <c r="R15" t="n">
         <v>10.6</v>
@@ -3075,37 +3142,37 @@
         <v>28.7</v>
       </c>
       <c r="T15" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="U15" t="n">
         <v>16.9</v>
       </c>
       <c r="V15" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W15" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA15" t="n">
         <v>21.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.2</v>
+        <v>93.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3126,10 +3193,10 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM15" t="n">
         <v>27</v>
@@ -3138,22 +3205,22 @@
         <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
@@ -3162,22 +3229,22 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3326,7 +3393,7 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR16" t="n">
         <v>25</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -3409,46 +3476,46 @@
         <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="L17" t="n">
         <v>6.1</v>
       </c>
       <c r="M17" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.365</v>
+        <v>0.369</v>
       </c>
       <c r="O17" t="n">
         <v>20.4</v>
       </c>
       <c r="P17" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="R17" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X17" t="n">
         <v>3.8</v>
@@ -3457,7 +3524,7 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="AA17" t="n">
         <v>23.1</v>
@@ -3466,13 +3533,13 @@
         <v>99.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3499,31 +3566,31 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
         <v>7</v>
       </c>
       <c r="AP17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
         <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>15</v>
@@ -3532,7 +3599,7 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -3573,61 +3640,61 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>0.305</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J18" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L18" t="n">
         <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P18" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R18" t="n">
         <v>12.3</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="U18" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V18" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W18" t="n">
         <v>6.6</v>
@@ -3639,19 +3706,19 @@
         <v>6.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="AA18" t="n">
         <v>20.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>-4.7</v>
+        <v>-4.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3672,7 +3739,7 @@
         <v>5</v>
       </c>
       <c r="AK18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
         <v>20</v>
@@ -3681,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
         <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
         <v>17</v>
@@ -3696,13 +3763,13 @@
         <v>5</v>
       </c>
       <c r="AS18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT18" t="n">
         <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
         <v>16</v>
@@ -3717,13 +3784,13 @@
         <v>30</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" t="n">
         <v>33</v>
       </c>
       <c r="G19" t="n">
-        <v>0.45</v>
+        <v>0.441</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
@@ -3782,25 +3849,25 @@
         <v>7.8</v>
       </c>
       <c r="M19" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O19" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P19" t="n">
         <v>24.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.784</v>
+        <v>0.781</v>
       </c>
       <c r="R19" t="n">
         <v>11</v>
       </c>
       <c r="S19" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T19" t="n">
         <v>40.5</v>
@@ -3812,10 +3879,10 @@
         <v>13.3</v>
       </c>
       <c r="W19" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
@@ -3827,22 +3894,22 @@
         <v>20.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
@@ -3854,25 +3921,25 @@
         <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL19" t="n">
         <v>7</v>
       </c>
       <c r="AM19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
         <v>15</v>
@@ -3890,7 +3957,7 @@
         <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>19</v>
@@ -3899,10 +3966,10 @@
         <v>17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB19" t="n">
         <v>20</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -4024,7 +4091,7 @@
         <v>7</v>
       </c>
       <c r="AG20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="n">
         <v>23</v>
@@ -4248,13 +4315,13 @@
         <v>7</v>
       </c>
       <c r="AU21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV21" t="n">
         <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4391,16 +4458,16 @@
         <v>27</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
         <v>29</v>
@@ -4409,16 +4476,16 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
         <v>8</v>
       </c>
       <c r="AP22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR22" t="n">
         <v>4</v>
@@ -4430,16 +4497,16 @@
         <v>3</v>
       </c>
       <c r="AU22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F23" t="n">
         <v>16</v>
       </c>
       <c r="G23" t="n">
-        <v>0.733</v>
+        <v>0.729</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4504,28 +4571,28 @@
         <v>78.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
         <v>10.4</v>
       </c>
       <c r="M23" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="N23" t="n">
         <v>0.392</v>
       </c>
       <c r="O23" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="P23" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.723</v>
+        <v>0.722</v>
       </c>
       <c r="R23" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S23" t="n">
         <v>32.9</v>
@@ -4534,13 +4601,13 @@
         <v>42.9</v>
       </c>
       <c r="U23" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="V23" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X23" t="n">
         <v>5.3</v>
@@ -4555,13 +4622,13 @@
         <v>22.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.3</v>
+        <v>102.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4576,10 +4643,10 @@
         <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
         <v>9</v>
@@ -4591,19 +4658,19 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="n">
         <v>10</v>
       </c>
       <c r="AP23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
@@ -4615,10 +4682,10 @@
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX23" t="n">
         <v>9</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>0.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF24" t="n">
         <v>16</v>
@@ -4755,7 +4822,7 @@
         <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI24" t="n">
         <v>18</v>
@@ -4776,16 +4843,16 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>27</v>
       </c>
       <c r="AR24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS24" t="n">
         <v>18</v>
@@ -4809,7 +4876,7 @@
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
         <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.576</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,46 +4932,46 @@
         <v>39.9</v>
       </c>
       <c r="J25" t="n">
-        <v>79.7</v>
+        <v>79.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.501</v>
+        <v>0.502</v>
       </c>
       <c r="L25" t="n">
         <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0.381</v>
+        <v>0.383</v>
       </c>
       <c r="O25" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="P25" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="Q25" t="n">
         <v>0.76</v>
       </c>
       <c r="R25" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S25" t="n">
         <v>31.3</v>
       </c>
       <c r="T25" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U25" t="n">
         <v>22.6</v>
       </c>
       <c r="V25" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="W25" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X25" t="n">
         <v>4.9</v>
@@ -4913,19 +4980,19 @@
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB25" t="n">
-        <v>107</v>
+        <v>107.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4961,7 +5028,7 @@
         <v>4</v>
       </c>
       <c r="AP25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ25" t="n">
         <v>20</v>
@@ -4982,7 +5049,7 @@
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
         <v>37</v>
       </c>
       <c r="F26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G26" t="n">
-        <v>0.638</v>
+        <v>0.627</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
@@ -5077,7 +5144,7 @@
         <v>28.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
         <v>20.6</v>
@@ -5089,46 +5156,46 @@
         <v>6.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
         <v>8</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5140,7 +5207,7 @@
         <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
@@ -5155,19 +5222,19 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AX26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY26" t="n">
         <v>2</v>
@@ -5179,7 +5246,7 @@
         <v>14</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" t="n">
         <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G27" t="n">
-        <v>0.21</v>
+        <v>0.213</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
@@ -5241,25 +5308,25 @@
         <v>18.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O27" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P27" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="Q27" t="n">
         <v>0.802</v>
       </c>
       <c r="R27" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S27" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T27" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="U27" t="n">
         <v>19.8</v>
@@ -5283,13 +5350,13 @@
         <v>21.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC27" t="n">
         <v>-9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5301,16 +5368,16 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
         <v>15</v>
@@ -5325,16 +5392,16 @@
         <v>6</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT27" t="n">
         <v>30</v>
@@ -5343,16 +5410,16 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AW27" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AX27" t="n">
         <v>26</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5492,10 +5559,10 @@
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM28" t="n">
         <v>8</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5519,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -5575,43 +5642,43 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
         <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>0.371</v>
+        <v>0.377</v>
       </c>
       <c r="H29" t="n">
         <v>48.2</v>
       </c>
       <c r="I29" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>79.7</v>
+        <v>79.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L29" t="n">
         <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O29" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P29" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="Q29" t="n">
         <v>0.83</v>
@@ -5623,19 +5690,19 @@
         <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="U29" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V29" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W29" t="n">
         <v>6.1</v>
       </c>
       <c r="X29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y29" t="n">
         <v>4.4</v>
@@ -5644,16 +5711,16 @@
         <v>19.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB29" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5671,7 +5738,7 @@
         <v>19</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="n">
         <v>13</v>
@@ -5689,7 +5756,7 @@
         <v>19</v>
       </c>
       <c r="AP29" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,16 +5765,16 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
@@ -5722,13 +5789,13 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
       </c>
       <c r="BC29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>8</v>
@@ -5874,16 +5941,16 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5892,16 +5959,16 @@
         <v>21</v>
       </c>
       <c r="AW30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>16</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA30" t="n">
         <v>1</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6038,7 +6105,7 @@
         <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-3-2008-09</t>
+          <t>2009-03-03</t>
         </is>
       </c>
     </row>
